--- a/acra_template.xlsx
+++ b/acra_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\dc01\06-OpSystDevDep\03-Documentation\CheckUp\For banks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grigo\OneDrive\Рабочий стол\ACRA Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="8BlITAcwucerOjxuX8DHEqtlIy+2s9tR6bzfIcT2Z2g8XdqyYuZAU6igW18M2haUYYEw5JCzOzQOoM8vVz0nzw==" workbookSaltValue="vosmzG5iYF5eSJxn+hD4tw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11640" tabRatio="664"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11640" tabRatio="664" firstSheet="1" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="PackageInfo" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
   <definedNames>
     <definedName name="Version">PackageInfo!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -253,7 +253,7 @@
     <t>Կապակցված վարկառուի ներքին իդենտիֆիկացման համար</t>
   </si>
   <si>
-    <t>TMP</t>
+    <t>ACC</t>
   </si>
 </sst>
 </file>
@@ -484,7 +484,7 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -500,9 +500,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -540,7 +540,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -612,7 +612,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -808,7 +808,7 @@
         <v>21</v>
       </c>
       <c r="B2" s="16">
-        <v>41757</v>
+        <v>46119</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -816,7 +816,7 @@
         <v>22</v>
       </c>
       <c r="B3" s="21">
-        <v>41763</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -824,7 +824,7 @@
         <v>23</v>
       </c>
       <c r="B4" s="22">
-        <v>41764.709085648145</v>
+        <v>46120.395833333336</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -880,7 +880,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="31" style="2" bestFit="1" customWidth="1"/>
@@ -972,6 +972,9 @@
         <v>27</v>
       </c>
     </row>
+    <row r="2" spans="1:21" customFormat="1"/>
+    <row r="3" spans="1:21" customFormat="1"/>
+    <row r="4" spans="1:21" customFormat="1"/>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="0fU47ECia8epkM3oKMmBhyHyGziHh5Ql0xGcwY14uudiXrzkQV0UjI/mWTe4uenO20Y2DgyRWsBwARqHaGdVFg==" saltValue="EC+419yyoMo93JVBhmLyVw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <sortState ref="A2:U7">
@@ -1133,7 +1136,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:Y4"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="31.42578125" style="5" bestFit="1" customWidth="1"/>
@@ -1241,6 +1244,9 @@
         <v>27</v>
       </c>
     </row>
+    <row r="2" spans="1:25" customFormat="1"/>
+    <row r="3" spans="1:25" customFormat="1"/>
+    <row r="4" spans="1:25" customFormat="1"/>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="4X5mnC0gE7ezGOlMwcejtcKJmcFda7vBW3V3wp+b53iDYaQRsfuHFemVn7U6zmB53ksk6C6V0RNPwniLvQ+Y5g==" saltValue="VLoSw/jMyn4BiHgO5hBiJQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <sortState ref="A2:Y8">
@@ -1256,7 +1262,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet10"/>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="27" style="2" bestFit="1" customWidth="1"/>
@@ -1283,6 +1289,14 @@
       <c r="E1" s="11" t="s">
         <v>49</v>
       </c>
+    </row>
+    <row r="2" spans="1:5" customFormat="1"/>
+    <row r="3" spans="1:5" customFormat="1"/>
+    <row r="4" spans="1:5">
+      <c r="A4"/>
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="23J5Nuc2Gm33cbuOWcboP21Ar18E8AkmHjmpRr0RtkEX9+uHP5XeH7z0O26Sm9dD16r2vhEbG7l21i2cSzMyIQ==" saltValue="/mcGb8GC+GpP6t29pf8DOw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
